--- a/artfynd/A 49052-2023 artfynd.xlsx
+++ b/artfynd/A 49052-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49052-2023 artfynd.xlsx
+++ b/artfynd/A 49052-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1117,6 +1117,324 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128533098</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92754</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>406604</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6855121</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128533100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92754</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>406599</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6854983</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128533099</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92742</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>406584</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6854982</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49052-2023 artfynd.xlsx
+++ b/artfynd/A 49052-2023 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>128533098</v>
       </c>
       <c r="B6" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128533100</v>
       </c>
       <c r="B7" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>128533099</v>
       </c>
       <c r="B8" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49052-2023 artfynd.xlsx
+++ b/artfynd/A 49052-2023 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>128533098</v>
       </c>
       <c r="B6" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128533100</v>
       </c>
       <c r="B7" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>128533099</v>
       </c>
       <c r="B8" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49052-2023 artfynd.xlsx
+++ b/artfynd/A 49052-2023 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>128533098</v>
       </c>
       <c r="B6" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128533100</v>
       </c>
       <c r="B7" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>128533099</v>
       </c>
       <c r="B8" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49052-2023 artfynd.xlsx
+++ b/artfynd/A 49052-2023 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>128533098</v>
       </c>
       <c r="B6" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128533100</v>
       </c>
       <c r="B7" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>128533099</v>
       </c>
       <c r="B8" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49052-2023 artfynd.xlsx
+++ b/artfynd/A 49052-2023 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>128533098</v>
       </c>
       <c r="B6" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128533100</v>
       </c>
       <c r="B7" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>128533099</v>
       </c>
       <c r="B8" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49052-2023 artfynd.xlsx
+++ b/artfynd/A 49052-2023 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>128533098</v>
       </c>
       <c r="B6" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128533100</v>
       </c>
       <c r="B7" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>128533099</v>
       </c>
       <c r="B8" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49052-2023 artfynd.xlsx
+++ b/artfynd/A 49052-2023 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>128533098</v>
       </c>
       <c r="B6" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128533100</v>
       </c>
       <c r="B7" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>128533099</v>
       </c>
       <c r="B8" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49052-2023 artfynd.xlsx
+++ b/artfynd/A 49052-2023 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>128533098</v>
       </c>
       <c r="B6" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128533100</v>
       </c>
       <c r="B7" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>128533099</v>
       </c>
       <c r="B8" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49052-2023 artfynd.xlsx
+++ b/artfynd/A 49052-2023 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>128533098</v>
       </c>
       <c r="B6" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128533100</v>
       </c>
       <c r="B7" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>128533099</v>
       </c>
       <c r="B8" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49052-2023 artfynd.xlsx
+++ b/artfynd/A 49052-2023 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>128533098</v>
       </c>
       <c r="B6" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128533100</v>
       </c>
       <c r="B7" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>128533099</v>
       </c>
       <c r="B8" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49052-2023 artfynd.xlsx
+++ b/artfynd/A 49052-2023 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>128533098</v>
       </c>
       <c r="B6" t="n">
-        <v>92823</v>
+        <v>92831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128533100</v>
       </c>
       <c r="B7" t="n">
-        <v>92823</v>
+        <v>92831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>128533099</v>
       </c>
       <c r="B8" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49052-2023 artfynd.xlsx
+++ b/artfynd/A 49052-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888669</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533099</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533098</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533100</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80564196</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888049</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1420,6 +1455,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113886830</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1526,8 +1566,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887062</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>